--- a/config/cartoes.example.xlsx
+++ b/config/cartoes.example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -421,6 +421,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,6 +464,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -484,6 +490,11 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -505,6 +516,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -528,6 +544,63 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>cartão cancelado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JKL_MN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BTG Pactual</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPQ_RS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Itaú</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
         </is>
       </c>
     </row>
